--- a/data/trans_dic/P62A$viudedad-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P62A$viudedad-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de viudedad</t>
+          <t>Población que, al menos, percibe una pensión de viudedad (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 5,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,92; 26,33</t>
+          <t>16,19; 26,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,19; 49,75</t>
+          <t>33,2; 49,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,07; 50,77</t>
+          <t>36,25; 51,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,41; 43,19</t>
+          <t>26,37; 42,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 11,49</t>
+          <t>5,82; 11,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,54; 22,19</t>
+          <t>13,56; 22,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,75; 24,09</t>
+          <t>15,54; 23,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 19,4</t>
+          <t>11,6; 19,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,06; 18,02</t>
+          <t>12,06; 17,93</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,14; 20,57</t>
+          <t>11,64; 20,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,66; 67,23</t>
+          <t>51,38; 67,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,13; 48,33</t>
+          <t>33,7; 47,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,45; 41,46</t>
+          <t>26,43; 41,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 11,04</t>
+          <t>5,37; 11,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,5; 29,43</t>
+          <t>20,09; 29,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,38; 23,17</t>
+          <t>15,1; 22,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 18,79</t>
+          <t>11,79; 18,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 14,96</t>
+          <t>9,24; 14,52</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 20,19</t>
+          <t>9,79; 19,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,3; 58,01</t>
+          <t>41,26; 58,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,28; 56,18</t>
+          <t>38,9; 57,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,44; 49,16</t>
+          <t>30,74; 49,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 14,11</t>
+          <t>1,46; 14,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,06; 26,77</t>
+          <t>17,34; 27,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,28; 27,26</t>
+          <t>17,76; 27,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 22,31</t>
+          <t>13,0; 22,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 15,2</t>
+          <t>3,34; 14,68</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,74; 19,01</t>
+          <t>10,66; 18,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,58; 54,25</t>
+          <t>38,48; 53,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,41; 49,59</t>
+          <t>35,45; 49,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,21; 43,06</t>
+          <t>29,78; 42,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,37</t>
+          <t>3,81; 8,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,87; 26,64</t>
+          <t>18,2; 26,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,16; 24,52</t>
+          <t>16,98; 24,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 21,07</t>
+          <t>14,19; 21,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,63</t>
+          <t>7,95; 12,74</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,98; 18,76</t>
+          <t>13,88; 18,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,97; 53,3</t>
+          <t>45,58; 53,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,81; 47,18</t>
+          <t>39,27; 46,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,94; 39,75</t>
+          <t>31,9; 39,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,94</t>
+          <t>3,18; 8,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,62; 24,17</t>
+          <t>19,55; 23,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,24; 22,3</t>
+          <t>18,26; 22,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,29; 18,06</t>
+          <t>14,41; 18,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 12,97</t>
+          <t>7,07; 12,91</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de viudedad</t>
+          <t>Población que, al menos, percibe una pensión de viudedad (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5812</t>
+          <t>0; 5221</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 10085</t>
+          <t>0; 11044</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1855</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28644; 47391</t>
+          <t>29134; 47824</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40770; 63009</t>
+          <t>42046; 62267</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57521; 83276</t>
+          <t>59460; 84647</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39389; 64399</t>
+          <t>39328; 63594</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9743; 19546</t>
+          <t>9901; 19636</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40322; 66086</t>
+          <t>40376; 66610</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59125; 90449</t>
+          <t>58361; 89525</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39306; 65698</t>
+          <t>39285; 65471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42200; 63070</t>
+          <t>42201; 62750</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5266</t>
+          <t>0; 5314</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4834</t>
+          <t>0; 4829</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4704</t>
+          <t>0; 5190</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22083; 40760</t>
+          <t>23065; 40559</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79243; 103118</t>
+          <t>78804; 103344</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71596; 101381</t>
+          <t>70693; 100488</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55950; 84526</t>
+          <t>53883; 84951</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9736; 20373</t>
+          <t>9906; 21325</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77067; 110630</t>
+          <t>75517; 109720</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70151; 105634</t>
+          <t>68872; 104820</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55013; 88011</t>
+          <t>55222; 87891</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35122; 57226</t>
+          <t>35357; 55549</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2187</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19709; 40550</t>
+          <t>19658; 39563</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49485; 69496</t>
+          <t>49432; 70654</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56610; 83068</t>
+          <t>57529; 84386</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42590; 66595</t>
+          <t>41641; 66887</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3588; 49037</t>
+          <t>5084; 51841</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46775; 73388</t>
+          <t>47548; 74294</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54703; 86294</t>
+          <t>56224; 87585</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39773; 70827</t>
+          <t>41286; 70250</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17820; 83365</t>
+          <t>18317; 80510</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1735</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2105</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1863</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23902; 42294</t>
+          <t>23709; 42118</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69761; 95617</t>
+          <t>67820; 93718</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81710; 111300</t>
+          <t>79573; 111369</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72630; 107059</t>
+          <t>74044; 106576</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8898; 19715</t>
+          <t>8972; 20868</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65430; 97530</t>
+          <t>66649; 98441</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>80486; 115004</t>
+          <t>79652; 114167</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72221; 108213</t>
+          <t>72895; 111126</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35718; 57866</t>
+          <t>36421; 58358</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6720</t>
+          <t>0; 6964</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 12367</t>
+          <t>0; 11249</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5579</t>
+          <t>0; 5233</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>112018; 150339</t>
+          <t>111262; 149374</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>259080; 307049</t>
+          <t>262575; 309304</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>297014; 352025</t>
+          <t>292984; 349248</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>235428; 293005</t>
+          <t>235152; 292433</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29687; 83784</t>
+          <t>29778; 83927</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>257740; 317638</t>
+          <t>256818; 314441</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>294999; 360593</t>
+          <t>295256; 361475</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>234046; 295889</t>
+          <t>236126; 298549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>125638; 225476</t>
+          <t>122995; 224531</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$viudedad-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P62A$viudedad-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,22</t>
+          <t>0,0; 4,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,19; 26,57</t>
+          <t>15,41; 25,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,2; 49,17</t>
+          <t>32,35; 49,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,25; 51,61</t>
+          <t>35,31; 52,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,37; 42,65</t>
+          <t>26,31; 43,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 11,54</t>
+          <t>5,65; 11,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,56; 22,37</t>
+          <t>13,56; 22,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,54; 23,84</t>
+          <t>15,25; 23,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 19,34</t>
+          <t>11,66; 19,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,06; 17,93</t>
+          <t>11,41; 17,13</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,64; 20,47</t>
+          <t>10,89; 20,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,38; 67,38</t>
+          <t>51,43; 66,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,7; 47,91</t>
+          <t>34,43; 49,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,43; 41,67</t>
+          <t>26,39; 40,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,56</t>
+          <t>5,13; 11,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,09; 29,19</t>
+          <t>20,13; 29,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,1; 22,99</t>
+          <t>15,49; 22,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,79; 18,76</t>
+          <t>11,89; 18,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 14,52</t>
+          <t>9,13; 14,59</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,79; 19,7</t>
+          <t>9,46; 18,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,26; 58,97</t>
+          <t>40,87; 58,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,9; 57,07</t>
+          <t>39,19; 55,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,74; 49,38</t>
+          <t>31,48; 49,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 14,92</t>
+          <t>9,02; 17,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,34; 27,1</t>
+          <t>17,42; 26,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,76; 27,66</t>
+          <t>16,84; 27,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,0; 22,12</t>
+          <t>12,97; 22,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 14,68</t>
+          <t>10,3; 16,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,66; 18,93</t>
+          <t>10,33; 18,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,48; 53,17</t>
+          <t>38,52; 54,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,45; 49,62</t>
+          <t>36,28; 49,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,78; 42,87</t>
+          <t>29,07; 42,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,86</t>
+          <t>3,92; 8,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,2; 26,89</t>
+          <t>18,41; 27,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 24,34</t>
+          <t>17,12; 24,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,19; 21,63</t>
+          <t>14,01; 21,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,74</t>
+          <t>7,69; 12,44</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1282,57 +1282,57 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,88; 18,64</t>
+          <t>13,36; 18,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,58; 53,69</t>
+          <t>45,35; 53,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,27; 46,81</t>
+          <t>39,83; 47,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,9; 39,68</t>
+          <t>32,11; 39,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,95</t>
+          <t>6,87; 9,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,55; 23,93</t>
+          <t>19,41; 23,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,26; 22,35</t>
+          <t>18,14; 22,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,41; 18,22</t>
+          <t>14,3; 18,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,07; 12,91</t>
+          <t>10,8; 13,58</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>39146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51816</t>
+          <t>53967</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5221</t>
+          <t>0; 4895</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 11044</t>
+          <t>0; 10250</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1660,47 +1660,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29134; 47824</t>
+          <t>30305; 49358</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42046; 62267</t>
+          <t>40968; 62947</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59460; 84647</t>
+          <t>57915; 85691</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39328; 63594</t>
+          <t>39237; 64295</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9901; 19636</t>
+          <t>10246; 20887</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40376; 66610</t>
+          <t>40384; 65775</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58361; 89525</t>
+          <t>57264; 89295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39285; 65471</t>
+          <t>39474; 65233</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42201; 62750</t>
+          <t>43135; 64726</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30974</t>
+          <t>33409</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45665</t>
+          <t>48964</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5314</t>
+          <t>0; 5711</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4829</t>
+          <t>0; 4904</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5190</t>
+          <t>0; 5075</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23065; 40559</t>
+          <t>23915; 44582</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78804; 103344</t>
+          <t>78892; 102625</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70693; 100488</t>
+          <t>72210; 102999</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53883; 84951</t>
+          <t>53797; 82558</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9906; 21325</t>
+          <t>10440; 22734</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>75517; 109720</t>
+          <t>75653; 110639</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68872; 104820</t>
+          <t>70644; 104016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55222; 87891</t>
+          <t>55692; 88949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35357; 55549</t>
+          <t>38624; 61718</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28337</t>
+          <t>30256</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47007</t>
+          <t>50870</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19658; 39563</t>
+          <t>21430; 41976</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49432; 70654</t>
+          <t>48963; 70267</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57529; 84386</t>
+          <t>57945; 82002</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41641; 66887</t>
+          <t>42637; 67384</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5084; 51841</t>
+          <t>14645; 28195</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47548; 74294</t>
+          <t>47759; 73989</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56224; 87585</t>
+          <t>53310; 87122</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41286; 70250</t>
+          <t>41168; 70304</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18317; 80510</t>
+          <t>40063; 64234</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32347</t>
+          <t>32564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>15174</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46093</t>
+          <t>47738</t>
         </is>
       </c>
     </row>
@@ -2284,47 +2284,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23709; 42118</t>
+          <t>23960; 41956</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67820; 93718</t>
+          <t>67899; 95250</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79573; 111369</t>
+          <t>81421; 112033</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>74044; 106576</t>
+          <t>72279; 106359</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8972; 20868</t>
+          <t>10074; 21711</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66649; 98441</t>
+          <t>67400; 99138</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79652; 114167</t>
+          <t>80298; 116654</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72895; 111126</t>
+          <t>71941; 111230</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36421; 58358</t>
+          <t>37550; 60787</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129604</t>
+          <t>135375</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>190581</t>
+          <t>201539</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6964</t>
+          <t>0; 6903</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 11249</t>
+          <t>0; 11048</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5233</t>
+          <t>0; 5593</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111262; 149374</t>
+          <t>116805; 157654</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>262575; 309304</t>
+          <t>261261; 309755</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>292984; 349248</t>
+          <t>297201; 351962</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>235152; 292433</t>
+          <t>236685; 291509</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29778; 83927</t>
+          <t>55192; 78578</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>256818; 314441</t>
+          <t>255092; 312903</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>295256; 361475</t>
+          <t>293362; 360159</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>236126; 298549</t>
+          <t>234246; 297540</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>122995; 224531</t>
+          <t>181275; 227978</t>
         </is>
       </c>
     </row>
